--- a/dados/excel/municipio_tempo.xlsx
+++ b/dados/excel/municipio_tempo.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -810,13 +810,13 @@
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>5410</v>
+        <v>5701</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>5812.81</v>
+        <v>5677.34</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>4599.99</v>
+        <v>4567.46</v>
       </c>
     </row>
     <row r="3">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>1894</v>
+        <v>2112</v>
       </c>
       <c r="D3" s="15" t="n">
-        <v>7176.19</v>
+        <v>7400.59</v>
       </c>
       <c r="E3" s="15" t="n">
-        <v>5579.04</v>
+        <v>5569.91</v>
       </c>
     </row>
     <row r="4">
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>3284</v>
+        <v>3305</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>9289.629999999999</v>
+        <v>9473.85</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>7602.6</v>
+        <v>7831.75</v>
       </c>
     </row>
     <row r="5">
@@ -873,13 +873,13 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1858</v>
+        <v>1885</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>12754.86</v>
+        <v>12753.55</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>11819.19</v>
+        <v>11574.68</v>
       </c>
     </row>
     <row r="6">
@@ -894,13 +894,13 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>13261.67</v>
+        <v>13016.47</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>12999.53</v>
+        <v>12559.64</v>
       </c>
     </row>
     <row r="7">
@@ -918,10 +918,10 @@
         <v>181</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>15488.92</v>
+        <v>15509.99</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>15685.39</v>
+        <v>15310.46</v>
       </c>
     </row>
     <row r="8">
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>13764.24</v>
+        <v>13620.99</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>11123.51</v>
+        <v>11002.08</v>
       </c>
     </row>
   </sheetData>
